--- a/DateBase/orders/Dang Nguyen 195_2026-5-12.xlsx
+++ b/DateBase/orders/Dang Nguyen 195_2026-5-12.xlsx
@@ -967,6 +967,9 @@
       <c r="G2" t="str">
         <v>0145.5122020151010158151510105010205100501010510510105510155105153315510155103335517121510202020</v>
       </c>
+      <c r="H2" t="str">
+        <v>CNY</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
